--- a/Bibsam_tidskriftslistor/scifree_data_oxford.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_oxford.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639FBD46-26D7-4AAD-B627-6B185EA2D293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F8AD3E-828F-4A34-A627-C08B88D1629E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="1656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3250" uniqueCount="1659">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -4988,6 +4988,15 @@
   </si>
   <si>
     <t>https://academic.oup.com/sd</t>
+  </si>
+  <si>
+    <t>1460-3578</t>
+  </si>
+  <si>
+    <t>Journal of Peace Research</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/jpr</t>
   </si>
 </sst>
 </file>
@@ -5054,8 +5063,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{29F4AE4F-3C6D-4BE0-8AAF-431A9A218867}" name="Table2" displayName="Table2" ref="A1:G531" totalsRowShown="0">
-  <autoFilter ref="A1:G531" xr:uid="{29F4AE4F-3C6D-4BE0-8AAF-431A9A218867}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{29F4AE4F-3C6D-4BE0-8AAF-431A9A218867}" name="Table2" displayName="Table2" ref="A1:G532" totalsRowShown="0">
+  <autoFilter ref="A1:G532" xr:uid="{29F4AE4F-3C6D-4BE0-8AAF-431A9A218867}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F5E2486E-E90D-461C-972F-7C4D25D666D5}" name="Imprint"/>
     <tableColumn id="2" xr3:uid="{4D955E89-3276-4531-A1BC-F7793CABE6EA}" name="ISSN Electronic"/>
@@ -5332,13 +5341,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34547141-E29C-4D3C-A0EC-D02E1559D016}">
-  <dimension ref="A1:G531"/>
+  <dimension ref="A1:G532"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="44.140625" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
@@ -8826,7 +8835,7 @@
         <v>288</v>
       </c>
       <c r="F172" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G172" t="s">
         <v>873</v>
@@ -15403,7 +15412,7 @@
         <v>419</v>
       </c>
       <c r="F495" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G495" t="s">
         <v>873</v>
@@ -16135,6 +16144,26 @@
         <v>871</v>
       </c>
       <c r="G531" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
+        <v>872</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D532" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E532" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F532" t="s">
+        <v>871</v>
+      </c>
+      <c r="G532" t="s">
         <v>873</v>
       </c>
     </row>
